--- a/model/param.xlsx
+++ b/model/param.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzapa\Desktop\Projekty\elektronika\Efekt overdrive\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzapa\Desktop\Projekty\elektronika\Ignis-overdrive\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DE3111D-C015-487F-B579-1CD082D41A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50641BF6-21EE-4BA6-B36C-E62B669C6AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>podstawa_a</t>
   </si>
@@ -129,6 +129,78 @@
   </si>
   <si>
     <t>input_wys</t>
+  </si>
+  <si>
+    <t>obudowa_MTS_otwor_D</t>
+  </si>
+  <si>
+    <t>obudowa_pot_rozstaw</t>
+  </si>
+  <si>
+    <t>obudowa_pot_poz_x</t>
+  </si>
+  <si>
+    <t>obudowa_pot_poz_y</t>
+  </si>
+  <si>
+    <t>obudowa_s_rozstaw_y</t>
+  </si>
+  <si>
+    <t>obudowa_s_rozstaw_x</t>
+  </si>
+  <si>
+    <t>obudowa_s_poz_y</t>
+  </si>
+  <si>
+    <t>obudowa_s_poz_x</t>
+  </si>
+  <si>
+    <t>obudowa_s_D</t>
+  </si>
+  <si>
+    <t>obudowa_s_rozstaw_x_poj</t>
+  </si>
+  <si>
+    <t>obudowa_pot_rozstaw_y</t>
+  </si>
+  <si>
+    <t>pcb_rozstaw_x</t>
+  </si>
+  <si>
+    <t>pcb_rozstaw_y</t>
+  </si>
+  <si>
+    <t>pcb_grubosc_scianki</t>
+  </si>
+  <si>
+    <t>pcb_poz_x</t>
+  </si>
+  <si>
+    <t>pcb_poz_y</t>
+  </si>
+  <si>
+    <t>pcb_wys_bloku</t>
+  </si>
+  <si>
+    <t>obudowa_footswitch_D</t>
+  </si>
+  <si>
+    <t>obudowa_footswitch_poz_x</t>
+  </si>
+  <si>
+    <t>obudowa_footswitch_poz_y</t>
+  </si>
+  <si>
+    <t>obudowa_led_indicator_D</t>
+  </si>
+  <si>
+    <t>obudowa_led_indicator_poz_x</t>
+  </si>
+  <si>
+    <t>obudowa_led_indicator_poz_y</t>
+  </si>
+  <si>
+    <t>obudowa_podkladka_otwory</t>
   </si>
 </sst>
 </file>
@@ -164,9 +236,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -447,18 +518,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="36.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1">
+      <c r="B1">
         <v>1.5</v>
       </c>
     </row>
@@ -466,7 +536,7 @@
       <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2">
         <v>4.5</v>
       </c>
     </row>
@@ -474,7 +544,7 @@
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3">
         <v>2.6</v>
       </c>
     </row>
@@ -482,7 +552,7 @@
       <c r="A4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4">
         <v>2.4</v>
       </c>
     </row>
@@ -490,7 +560,7 @@
       <c r="A5" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5">
         <v>5.5</v>
       </c>
     </row>
@@ -498,23 +568,23 @@
       <c r="A6" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="1">
-        <v>120</v>
+      <c r="B6">
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="1">
-        <v>65</v>
+      <c r="B7">
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8">
         <v>2</v>
       </c>
     </row>
@@ -522,7 +592,7 @@
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9">
         <v>4</v>
       </c>
     </row>
@@ -530,7 +600,7 @@
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10">
         <v>4</v>
       </c>
     </row>
@@ -538,7 +608,7 @@
       <c r="A11" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11">
         <v>3</v>
       </c>
     </row>
@@ -546,33 +616,33 @@
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12">
         <f>B6</f>
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13">
         <f>B7</f>
-        <v>65</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>10</v>
       </c>
-      <c r="B14" s="1">
-        <v>36</v>
+      <c r="B14">
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15">
         <v>2</v>
       </c>
     </row>
@@ -580,7 +650,7 @@
       <c r="A16" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16">
         <v>38</v>
       </c>
     </row>
@@ -588,7 +658,7 @@
       <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17">
         <v>4</v>
       </c>
     </row>
@@ -596,7 +666,7 @@
       <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18">
         <v>4</v>
       </c>
     </row>
@@ -604,7 +674,7 @@
       <c r="A19" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19">
         <v>8</v>
       </c>
     </row>
@@ -612,7 +682,7 @@
       <c r="A20" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20">
         <v>8</v>
       </c>
     </row>
@@ -620,7 +690,7 @@
       <c r="A21" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21">
         <f>B11</f>
         <v>3</v>
       </c>
@@ -629,7 +699,7 @@
       <c r="A22" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22">
         <v>11.5</v>
       </c>
     </row>
@@ -637,23 +707,23 @@
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="1">
-        <v>15</v>
+      <c r="B23">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="1">
-        <v>80</v>
+      <c r="B24">
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25">
         <v>11.5</v>
       </c>
     </row>
@@ -661,49 +731,241 @@
       <c r="A26" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26">
         <f>B23</f>
-        <v>15</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="1">
-        <v>100</v>
+      <c r="B27">
+        <v>38</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28">
         <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1">
-        <v>9</v>
+        <v>32</v>
+      </c>
+      <c r="B29">
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1">
-        <v>14.4</v>
+        <v>41</v>
+      </c>
+      <c r="B30">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+      <c r="B34">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>28</v>
+      </c>
+      <c r="B39">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>29</v>
+      </c>
+      <c r="B40">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
         <v>30</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B41">
         <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>31</v>
+      </c>
+      <c r="B42">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>47</v>
+      </c>
+      <c r="B46">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/model/param.xlsx
+++ b/model/param.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzapa\Desktop\Projekty\elektronika\Ignis-overdrive\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50641BF6-21EE-4BA6-B36C-E62B669C6AA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2012B671-57D6-4DE0-8D3A-CF746597428E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
   <si>
     <t>podstawa_a</t>
   </si>
@@ -201,6 +201,75 @@
   </si>
   <si>
     <t>obudowa_podkladka_otwory</t>
+  </si>
+  <si>
+    <t>obudowa_uchwyt_grubosc</t>
+  </si>
+  <si>
+    <t>obudowa_uchwyt_szerokosc_wew</t>
+  </si>
+  <si>
+    <t>obudowa_uchwyt_wysokosc_wew</t>
+  </si>
+  <si>
+    <t>obudowa_gniazdo_poz</t>
+  </si>
+  <si>
+    <t>obudowa_uchwyt_kolnierz_wys</t>
+  </si>
+  <si>
+    <t>obudowa_uchwyt_poz_x</t>
+  </si>
+  <si>
+    <t>obudowa_uchwyt_poz_z</t>
+  </si>
+  <si>
+    <t>obudowa_podciecie_inout_wys</t>
+  </si>
+  <si>
+    <t>obudowa_podciecie_logo_wys</t>
+  </si>
+  <si>
+    <t>obudowa_podciecie_logo_szerokosc</t>
+  </si>
+  <si>
+    <t>obudowa_pot_pozycjonowanie_szerokosc</t>
+  </si>
+  <si>
+    <t>obudowa_pot_pozycjonowanie_wys</t>
+  </si>
+  <si>
+    <t>obudowa_pot_pozycjonowanie_glebokosc</t>
+  </si>
+  <si>
+    <t>obudowa_led_mocowanie_wys</t>
+  </si>
+  <si>
+    <t>obudowa_led_mocowanie_grubosc</t>
+  </si>
+  <si>
+    <t>obudowa_led_mocowanie_odstep</t>
+  </si>
+  <si>
+    <t>obudowa_led_mocowanie_dlugosc_B</t>
+  </si>
+  <si>
+    <t>obudowa_led_mocowanie_rozstaw_otworow</t>
+  </si>
+  <si>
+    <t>holder_led_grubosc</t>
+  </si>
+  <si>
+    <t>holder_led_dlugosc</t>
+  </si>
+  <si>
+    <t>holder_led_uchwyt_D</t>
+  </si>
+  <si>
+    <t>holder_led_uchwyt_szerokosc</t>
+  </si>
+  <si>
+    <t>holder_led_uchwyt_wysokosc</t>
   </si>
 </sst>
 </file>
@@ -518,10 +587,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B55"/>
+  <dimension ref="A1:B78"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -553,7 +622,7 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -561,7 +630,7 @@
         <v>18</v>
       </c>
       <c r="B5">
-        <v>5.5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -700,7 +769,7 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -724,7 +793,8 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>11.5</v>
+        <f>B22</f>
+        <v>12</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
@@ -749,7 +819,7 @@
         <v>27</v>
       </c>
       <c r="B28">
-        <v>8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
@@ -837,7 +907,7 @@
         <v>28</v>
       </c>
       <c r="B39">
-        <v>9</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -853,7 +923,7 @@
         <v>30</v>
       </c>
       <c r="B41">
-        <v>11</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -909,7 +979,7 @@
         <v>46</v>
       </c>
       <c r="B48">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -941,7 +1011,7 @@
         <v>51</v>
       </c>
       <c r="B52">
-        <v>4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -966,6 +1036,190 @@
       </c>
       <c r="B55">
         <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>56</v>
+      </c>
+      <c r="B59">
+        <v>17.5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60">
+        <v>26.3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>58</v>
+      </c>
+      <c r="B62">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/model/param.xlsx
+++ b/model/param.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zzapa\Desktop\Projekty\elektronika\Ignis-overdrive\model\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2012B671-57D6-4DE0-8D3A-CF746597428E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD437F67-96C0-4D23-9732-C1AD958C2AE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>podstawa_a</t>
   </si>
@@ -270,6 +270,39 @@
   </si>
   <si>
     <t>holder_led_uchwyt_wysokosc</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_grubosc</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_a</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_b</t>
+  </si>
+  <si>
+    <t>podstawa_mocowanie_DC_a</t>
+  </si>
+  <si>
+    <t>podstawa_mocowanie_DC_b</t>
+  </si>
+  <si>
+    <t>podstawa_mocowanie_DC_wys</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_odleglosc_miedzy_ramionami</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_dlugosc_ramion</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_grubosc_ramion</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_wys</t>
+  </si>
+  <si>
+    <t>holder_gniazdo_uchwyt_poz</t>
   </si>
 </sst>
 </file>
@@ -587,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.44140625" bestFit="1" customWidth="1"/>
@@ -1222,6 +1255,94 @@
         <v>5</v>
       </c>
     </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>84</v>
+      </c>
+      <c r="B82">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>85</v>
+      </c>
+      <c r="B83">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>86</v>
+      </c>
+      <c r="B84">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>87</v>
+      </c>
+      <c r="B85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>88</v>
+      </c>
+      <c r="B86">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>81</v>
+      </c>
+      <c r="B87">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>82</v>
+      </c>
+      <c r="B88">
+        <v>8.9</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>83</v>
+      </c>
+      <c r="B89">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
